--- a/Smith_Jungers_1997/Smith_Jungers_1997_registry_rows.xlsx
+++ b/Smith_Jungers_1997/Smith_Jungers_1997_registry_rows.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="R1da780c4fefb4b06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="R4cfec583d1a24cbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="R2afef62b08444ccf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="Ra6d05035b2a64888"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="R7cb81a57f572436b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="R851ec49524824fa7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -333,7 +333,7 @@
         <x:v>Adult body mass; sex-specific estimates and sample sizes</x:v>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>Source tables / results to select</x:v>
+        <x:v>Table 5: Body mass of extant primates</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
         <x:v>HOLD — existing compilation coverage first
@@ -350,13 +350,13 @@
         <x:v>Nicholas Saddler dissertation: Methods, Table 2 note and References (local final dissertation). Kamilar_Cooper_2013/reference_tables/Kamilar_Cooper_2013_S2_references.csv (Mass_ref).</x:v>
       </x:c>
       <x:c r="H2" s="3" t="str">
-        <x:v>Unresolved — full text needed before assigning an item number</x:v>
+        <x:v>Verified in EndNote full text — PDF pp. 16–26 / printed pp. 538–548, including continuations. Preserve male/female values, sample sizes, wild/captive status and references; consult explanatory notes and appendix. Reuse values already covered by existing compilations.</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>Full text not obtained — item cannot yet be verified</x:v>
+        <x:v>Existing full-text PDF verified in EndNote; original retained</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>Not obtained</x:v>
+        <x:v>/Users/crossmodal/Documents/References.Data/PDF/1038828825/Smith-1997-Body mass in compara.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -514,7 +514,9 @@
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="3"/>
-      <x:c r="D2" s="3"/>
+      <x:c r="D2" s="3" t="str">
+        <x:v>Table 5</x:v>
+      </x:c>
       <x:c r="E2" s="6"/>
       <x:c r="F2" s="6"/>
       <x:c r="G2" s="6"/>
@@ -525,11 +527,11 @@
       <x:c r="L2" s="6"/>
       <x:c r="M2" s="6"/>
       <x:c r="N2" s="3" t="str">
-        <x:v>Article tables/figures/text (not extracted)</x:v>
+        <x:v>Existing EndNote full-text PDF verified; no dataset extraction</x:v>
       </x:c>
       <x:c r="O2" s="3" t="str">
         <x:v>Nick: explicit body-mass source. Planned folder: Smith_Jungers_1997. Target: Source tables / results to select. Overlap review before extraction. Values already occur indirectly in Powell 2017 and Kamilar–Cooper 2013. Resolve sample, sex, population and primary source before claiming new coverage.
-Item check 2026-10-25: Unresolved — full text needed before assigning an item number. Availability: Full text not obtained — item cannot yet be verified.</x:v>
+EndNote correction 2026-10-25: Verified in EndNote full text — PDF pp. 16–26 / printed pp. 538–548, including continuations. Preserve male/female values, sample sizes, wild/captive status and references; consult explanatory notes and appendix. Reuse values already covered by existing compilations. Local PDF: /Users/crossmodal/Documents/References.Data/PDF/1038828825/Smith-1997-Body mass in compara.pdf</x:v>
       </x:c>
       <x:c r="P2" s="3" t="str">
         <x:v>HOLD — existing compilation coverage first</x:v>
@@ -705,7 +707,7 @@
         <x:v>Unresolved items</x:v>
       </x:c>
       <x:c r="B15" s="3" t="str">
-        <x:v>Blank Item number means either full text is still required or a review is REFERENCE ONLY. Smaers 2013 Table 1 is retained from earlier identification but has not been reverified from a locally acquired full text. Human snapshot checks remain pending.</x:v>
+        <x:v>Blank Item number means full text is still required or the source is REFERENCE ONLY. The six EndNote PDFs identified on 2026-10-25 are linked in Source list and their source-folder notes. Smaers 2013 Table 1 is now verified. Human snapshot checks remain pending.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -989,13 +991,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEB4303C-6E7C-4265-AC2D-2112D6A92B82}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC44AE31-761D-428A-B7D3-4AA78A19406D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94969966-AA93-44B3-B846-6B8472022809}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4190784-94C5-42F1-83B7-6470B9D95AED}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0F95AC3-6BE6-46BC-8C1A-B59F8D404E9F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF0DFA85-216E-4E82-B72E-D20C2C58FBA2}"/>
 </file>